--- a/game_config/Datas/DropTableConfig.xlsx
+++ b/game_config/Datas/DropTableConfig.xlsx
@@ -523,14 +523,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="14.4" ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -556,7 +556,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -582,7 +582,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -608,7 +608,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -634,7 +634,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>1001</v>
       </c>
@@ -642,7 +642,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>1001</v>
+        <v>1201</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -651,13 +651,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>1002</v>
       </c>
@@ -665,7 +665,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>1101</v>
+        <v>1001</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -674,18 +674,18 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="H6" s="2">
-        <v>5106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ac:dyDescent="0.25">
       <c r="B7" s="2">
-        <v>2001</v>
+        <v>1003</v>
       </c>
       <c r="C7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2">
         <v>1002</v>
@@ -697,15 +697,107 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
+        <v>50</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ac:dyDescent="0.25">
+      <c r="B8" s="2">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1101</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
         <v>1000</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H8" s="2">
+        <v>5106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ac:dyDescent="0.25">
+      <c r="B9" s="2">
+        <v>2001</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1201</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>800</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ac:dyDescent="0.25">
+      <c r="B10" s="2">
+        <v>2002</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1001</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>150</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ac:dyDescent="0.25">
+      <c r="B11" s="2">
+        <v>2003</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1002</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>50</v>
+      </c>
+      <c r="H11" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
 </worksheet>
 </file>
--- a/game_config/Datas/DropTableConfig.xlsx
+++ b/game_config/Datas/DropTableConfig.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809FF718-D350-486F-AAC0-3E4292CCBECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44709B1D-5052-4E3D-A8E1-626EEA7410A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DropTableConfig" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -33,117 +34,24 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>model_id</t>
-  </si>
-  <si>
-    <t>max_hp</t>
-  </si>
-  <si>
-    <t>max_mp</t>
-  </si>
-  <si>
-    <t>attack_damage</t>
-  </si>
-  <si>
-    <t>move_speed</t>
-  </si>
-  <si>
-    <t>attack_range</t>
-  </si>
-  <si>
-    <t>attack_interval_ms</t>
-  </si>
-  <si>
-    <t>attack_mode</t>
-  </si>
-  <si>
-    <t>skill_id</t>
-  </si>
-  <si>
-    <t>respawn_seconds</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
-    <t>c,s</t>
-  </si>
-  <si>
     <t>s</t>
   </si>
   <si>
     <t>##</t>
   </si>
   <si>
-    <t>怪物配置ID</t>
-  </si>
-  <si>
-    <t>显示名称</t>
-  </si>
-  <si>
-    <t>客户端模型标识</t>
-  </si>
-  <si>
-    <t>基础最大生命值</t>
-  </si>
-  <si>
-    <t>基础最大魔法值</t>
-  </si>
-  <si>
-    <t>基础攻击伤害</t>
-  </si>
-  <si>
-    <t>每秒移动米数</t>
-  </si>
-  <si>
-    <t>普通攻击距离（米）</t>
-  </si>
-  <si>
-    <t>普通攻击间隔（毫秒）</t>
-  </si>
-  <si>
-    <t>攻击模式：0被动，1主动</t>
-  </si>
-  <si>
-    <t>技能配置ID：当前演示0表示普通攻击</t>
-  </si>
-  <si>
-    <t>死亡后重生秒数</t>
-  </si>
-  <si>
-    <t>怪A</t>
-  </si>
-  <si>
-    <t>monster/dummy</t>
-  </si>
-  <si>
-    <t>怪B</t>
-  </si>
-  <si>
-    <t>monster/wolf</t>
-  </si>
-  <si>
     <t>drop_table_id</t>
   </si>
   <si>
-    <t>掉落表配置ID；0表示不生成掉落</t>
-  </si>
-  <si>
     <t>item_config_id</t>
   </si>
   <si>
@@ -178,6 +86,12 @@
   </si>
   <si>
     <t>任务目标ID；0表示普通掉落</t>
+  </si>
+  <si>
+    <t>gold</t>
+  </si>
+  <si>
+    <t>铜币数量；0表示道具掉落</t>
   </si>
 </sst>
 </file>
@@ -523,281 +437,397 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="14.4" ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="H4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1201</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>800</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1001</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>150</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1002</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ac:dyDescent="0.25">
-      <c r="B5" s="2">
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1101</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1000</v>
+      </c>
+      <c r="H8">
+        <v>5106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>2001</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>1201</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>800</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>2002</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
         <v>1001</v>
       </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1201</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2">
-        <v>800</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ac:dyDescent="0.25">
-      <c r="B6" s="2">
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>150</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>2003</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
         <v>1002</v>
       </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>50</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>3001</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
         <v>1001</v>
       </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>3002</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>1002</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>1000</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>3003</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>1003</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>1000</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>3004</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>1000</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>150</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ac:dyDescent="0.25">
-      <c r="B7" s="2">
-        <v>1003</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1002</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2">
-        <v>50</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ac:dyDescent="0.25">
-      <c r="B8" s="2">
-        <v>1004</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1101</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="H8" s="2">
-        <v>5106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ac:dyDescent="0.25">
-      <c r="B9" s="2">
-        <v>2001</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1201</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2">
-        <v>800</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ac:dyDescent="0.25">
-      <c r="B10" s="2">
-        <v>2002</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1001</v>
-      </c>
-      <c r="E10" s="2">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2">
-        <v>150</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ac:dyDescent="0.25">
-      <c r="B11" s="2">
-        <v>2003</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1002</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2">
-        <v>50</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>